--- a/Catch models/msy_resumo_cenarios_cmsy.xlsx
+++ b/Catch models/msy_resumo_cenarios_cmsy.xlsx
@@ -486,13 +486,13 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>1730.647378368045</v>
+        <v>1252.5365223986</v>
       </c>
       <c r="E2">
-        <v>1282.74848422246</v>
+        <v>1013.0797295623</v>
       </c>
       <c r="F2">
-        <v>2488.96524488205</v>
+        <v>1564.436875354717</v>
       </c>
       <c r="G2">
         <v>6000</v>
@@ -509,13 +509,13 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>1878.980225505375</v>
+        <v>1427.20837159651</v>
       </c>
       <c r="E3">
-        <v>1602.1847029827</v>
+        <v>1247.16784020668</v>
       </c>
       <c r="F3">
-        <v>2183.211526000468</v>
+        <v>1693.05094449004</v>
       </c>
       <c r="G3">
         <v>6000</v>
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>2010.82082157279</v>
+        <v>1578.35841866223</v>
       </c>
       <c r="E4">
-        <v>1377.17906583666</v>
+        <v>1081.63617882071</v>
       </c>
       <c r="F4">
-        <v>2948.607567771776</v>
+        <v>2325.16306915389</v>
       </c>
       <c r="G4">
         <v>6000</v>
@@ -555,13 +555,13 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>1691.24563515584</v>
+        <v>1285.21126909667</v>
       </c>
       <c r="E5">
-        <v>1286.56966022438</v>
+        <v>949.6926472250091</v>
       </c>
       <c r="F5">
-        <v>2360.953822847496</v>
+        <v>1812.044829182426</v>
       </c>
       <c r="G5">
         <v>6000</v>
@@ -578,13 +578,13 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>1937.654237838485</v>
+        <v>1288.70090730588</v>
       </c>
       <c r="E6">
-        <v>1409.455544059662</v>
+        <v>1047.869999890413</v>
       </c>
       <c r="F6">
-        <v>2746.56488321551</v>
+        <v>1606.04744454232</v>
       </c>
       <c r="G6">
         <v>6000</v>
@@ -601,13 +601,13 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <v>2030.3241540224</v>
+        <v>1435.071618454</v>
       </c>
       <c r="E7">
-        <v>1714.125400405922</v>
+        <v>1226.81938286894</v>
       </c>
       <c r="F7">
-        <v>2491.310135168238</v>
+        <v>1670.335448234624</v>
       </c>
       <c r="G7">
         <v>6000</v>
@@ -624,13 +624,13 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>2146.7007102959</v>
+        <v>1542.95874271649</v>
       </c>
       <c r="E8">
-        <v>1436.273330597549</v>
+        <v>1056.600187994776</v>
       </c>
       <c r="F8">
-        <v>3160.902924726345</v>
+        <v>2337.919975496961</v>
       </c>
       <c r="G8">
         <v>6000</v>
@@ -647,13 +647,13 @@
         <v>15</v>
       </c>
       <c r="D9">
-        <v>1927.34148567465</v>
+        <v>1284.5040280893</v>
       </c>
       <c r="E9">
-        <v>1400.05686591663</v>
+        <v>941.578443503317</v>
       </c>
       <c r="F9">
-        <v>2711.56235268858</v>
+        <v>1869.798899886674</v>
       </c>
       <c r="G9">
         <v>6000</v>
@@ -670,13 +670,13 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>2051.41854168801</v>
+        <v>1312.2419440263</v>
       </c>
       <c r="E10">
-        <v>1425.129495181626</v>
+        <v>1040.87683968676</v>
       </c>
       <c r="F10">
-        <v>3079.20201596889</v>
+        <v>1719.95311067138</v>
       </c>
       <c r="G10">
         <v>6000</v>
@@ -693,13 +693,13 @@
         <v>11</v>
       </c>
       <c r="D11">
-        <v>2090.50106640643</v>
+        <v>1459.96651021782</v>
       </c>
       <c r="E11">
-        <v>1722.603311476352</v>
+        <v>1245.07514783672</v>
       </c>
       <c r="F11">
-        <v>2815.677429469179</v>
+        <v>1723.0838491068</v>
       </c>
       <c r="G11">
         <v>6000</v>
@@ -716,13 +716,13 @@
         <v>13</v>
       </c>
       <c r="D12">
-        <v>2160.54177626098</v>
+        <v>1544.239281356015</v>
       </c>
       <c r="E12">
-        <v>1449.86586754235</v>
+        <v>1041.18268688601</v>
       </c>
       <c r="F12">
-        <v>3285.944948116742</v>
+        <v>2291.869639886179</v>
       </c>
       <c r="G12">
         <v>6000</v>
@@ -739,13 +739,13 @@
         <v>15</v>
       </c>
       <c r="D13">
-        <v>2003.5854500475</v>
+        <v>1479.07880947101</v>
       </c>
       <c r="E13">
-        <v>1330.843325429259</v>
+        <v>1101.85162753606</v>
       </c>
       <c r="F13">
-        <v>2956.030779032498</v>
+        <v>2062.203152736005</v>
       </c>
       <c r="G13">
         <v>6000</v>
@@ -762,13 +762,13 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>1910.44556871566</v>
+        <v>1260.73744343646</v>
       </c>
       <c r="E14">
-        <v>1387.06290167743</v>
+        <v>1015.252993158847</v>
       </c>
       <c r="F14">
-        <v>2772.291961463751</v>
+        <v>1592.27381902794</v>
       </c>
       <c r="G14">
         <v>6000</v>
@@ -785,13 +785,13 @@
         <v>11</v>
       </c>
       <c r="D15">
-        <v>2009.52131217528</v>
+        <v>1423.18198601764</v>
       </c>
       <c r="E15">
-        <v>1678.51230993865</v>
+        <v>1235.01541949573</v>
       </c>
       <c r="F15">
-        <v>2535.020627653065</v>
+        <v>1661.06879551554</v>
       </c>
       <c r="G15">
         <v>6000</v>
@@ -808,13 +808,13 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <v>2164.59122540205</v>
+        <v>1474.612563035055</v>
       </c>
       <c r="E16">
-        <v>1423.849001776728</v>
+        <v>989.190350954937</v>
       </c>
       <c r="F16">
-        <v>3156.60035237706</v>
+        <v>2249.58471225305</v>
       </c>
       <c r="G16">
         <v>6000</v>
@@ -831,13 +831,13 @@
         <v>15</v>
       </c>
       <c r="D17">
-        <v>1844.82073353007</v>
+        <v>1337.7031280299</v>
       </c>
       <c r="E17">
-        <v>1341.178148906426</v>
+        <v>952.1233318391405</v>
       </c>
       <c r="F17">
-        <v>2603.627663282703</v>
+        <v>1948.631580614323</v>
       </c>
       <c r="G17">
         <v>6000</v>

--- a/Catch models/msy_resumo_cenarios_cmsy.xlsx
+++ b/Catch models/msy_resumo_cenarios_cmsy.xlsx
@@ -486,13 +486,13 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>1252.5365223986</v>
+        <v>1685.48383583328</v>
       </c>
       <c r="E2">
-        <v>1013.0797295623</v>
+        <v>1349.149689804463</v>
       </c>
       <c r="F2">
-        <v>1564.436875354717</v>
+        <v>2078.770458384804</v>
       </c>
       <c r="G2">
         <v>6000</v>
@@ -509,13 +509,13 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>1427.20837159651</v>
+        <v>1920.69952928994</v>
       </c>
       <c r="E3">
-        <v>1247.16784020668</v>
+        <v>1683.781841405284</v>
       </c>
       <c r="F3">
-        <v>1693.05094449004</v>
+        <v>2181.211737133239</v>
       </c>
       <c r="G3">
         <v>6000</v>
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>1578.35841866223</v>
+        <v>1905.28063232423</v>
       </c>
       <c r="E4">
-        <v>1081.63617882071</v>
+        <v>1295.92039717895</v>
       </c>
       <c r="F4">
-        <v>2325.16306915389</v>
+        <v>2748.64493962449</v>
       </c>
       <c r="G4">
         <v>6000</v>
@@ -555,13 +555,13 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>1285.21126909667</v>
+        <v>1509.19386341416</v>
       </c>
       <c r="E5">
-        <v>949.6926472250091</v>
+        <v>1105.958808609553</v>
       </c>
       <c r="F5">
-        <v>1812.044829182426</v>
+        <v>2137.24943536719</v>
       </c>
       <c r="G5">
         <v>6000</v>
@@ -578,13 +578,13 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>1288.70090730588</v>
+        <v>1680.239370685315</v>
       </c>
       <c r="E6">
-        <v>1047.869999890413</v>
+        <v>1337.84500257344</v>
       </c>
       <c r="F6">
-        <v>1606.04744454232</v>
+        <v>2072.26952522193</v>
       </c>
       <c r="G6">
         <v>6000</v>
@@ -601,13 +601,13 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <v>1435.071618454</v>
+        <v>1907.976256733</v>
       </c>
       <c r="E7">
-        <v>1226.81938286894</v>
+        <v>1669.163054643006</v>
       </c>
       <c r="F7">
-        <v>1670.335448234624</v>
+        <v>2176.95024837607</v>
       </c>
       <c r="G7">
         <v>6000</v>
@@ -624,13 +624,13 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>1542.95874271649</v>
+        <v>1823.22707232206</v>
       </c>
       <c r="E8">
-        <v>1056.600187994776</v>
+        <v>1236.606279263052</v>
       </c>
       <c r="F8">
-        <v>2337.919975496961</v>
+        <v>2771.63846275837</v>
       </c>
       <c r="G8">
         <v>6000</v>
@@ -647,13 +647,13 @@
         <v>15</v>
       </c>
       <c r="D9">
-        <v>1284.5040280893</v>
+        <v>1661.14407908697</v>
       </c>
       <c r="E9">
-        <v>941.578443503317</v>
+        <v>1257.40589568261</v>
       </c>
       <c r="F9">
-        <v>1869.798899886674</v>
+        <v>2298.73873257972</v>
       </c>
       <c r="G9">
         <v>6000</v>
@@ -670,13 +670,13 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>1312.2419440263</v>
+        <v>1708.36195530609</v>
       </c>
       <c r="E10">
-        <v>1040.87683968676</v>
+        <v>1379.75152781912</v>
       </c>
       <c r="F10">
-        <v>1719.95311067138</v>
+        <v>2085.6583110044</v>
       </c>
       <c r="G10">
         <v>6000</v>
@@ -693,13 +693,13 @@
         <v>11</v>
       </c>
       <c r="D11">
-        <v>1459.96651021782</v>
+        <v>1949.51835765636</v>
       </c>
       <c r="E11">
-        <v>1245.07514783672</v>
+        <v>1683.254645586574</v>
       </c>
       <c r="F11">
-        <v>1723.0838491068</v>
+        <v>2233.09483066826</v>
       </c>
       <c r="G11">
         <v>6000</v>
@@ -716,13 +716,13 @@
         <v>13</v>
       </c>
       <c r="D12">
-        <v>1544.239281356015</v>
+        <v>1848.5244396762</v>
       </c>
       <c r="E12">
-        <v>1041.18268688601</v>
+        <v>1271.212896572069</v>
       </c>
       <c r="F12">
-        <v>2291.869639886179</v>
+        <v>2802.74923966572</v>
       </c>
       <c r="G12">
         <v>6000</v>
@@ -739,13 +739,13 @@
         <v>15</v>
       </c>
       <c r="D13">
-        <v>1479.07880947101</v>
+        <v>1595.08738026127</v>
       </c>
       <c r="E13">
-        <v>1101.85162753606</v>
+        <v>1161.822316106932</v>
       </c>
       <c r="F13">
-        <v>2062.203152736005</v>
+        <v>2253.38604822688</v>
       </c>
       <c r="G13">
         <v>6000</v>
@@ -762,13 +762,13 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>1260.73744343646</v>
+        <v>1678.9510387947</v>
       </c>
       <c r="E14">
-        <v>1015.252993158847</v>
+        <v>1365.273451346336</v>
       </c>
       <c r="F14">
-        <v>1592.27381902794</v>
+        <v>2069.71664611423</v>
       </c>
       <c r="G14">
         <v>6000</v>
@@ -785,13 +785,13 @@
         <v>11</v>
       </c>
       <c r="D15">
-        <v>1423.18198601764</v>
+        <v>1927.90827336451</v>
       </c>
       <c r="E15">
-        <v>1235.01541949573</v>
+        <v>1671.07898622216</v>
       </c>
       <c r="F15">
-        <v>1661.06879551554</v>
+        <v>2208.55017897042</v>
       </c>
       <c r="G15">
         <v>6000</v>
@@ -808,13 +808,13 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <v>1474.612563035055</v>
+        <v>1738.882909077935</v>
       </c>
       <c r="E16">
-        <v>989.190350954937</v>
+        <v>1156.459866758332</v>
       </c>
       <c r="F16">
-        <v>2249.58471225305</v>
+        <v>2683.810562105051</v>
       </c>
       <c r="G16">
         <v>6000</v>
@@ -831,13 +831,13 @@
         <v>15</v>
       </c>
       <c r="D17">
-        <v>1337.7031280299</v>
+        <v>1778.19401436755</v>
       </c>
       <c r="E17">
-        <v>952.1233318391405</v>
+        <v>1395.71950887412</v>
       </c>
       <c r="F17">
-        <v>1948.631580614323</v>
+        <v>2441.37156360483</v>
       </c>
       <c r="G17">
         <v>6000</v>

--- a/Catch models/msy_resumo_cenarios_cmsy.xlsx
+++ b/Catch models/msy_resumo_cenarios_cmsy.xlsx
@@ -486,13 +486,13 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>1685.48383583328</v>
+        <v>1714.805965986315</v>
       </c>
       <c r="E2">
-        <v>1349.149689804463</v>
+        <v>1378.98162613127</v>
       </c>
       <c r="F2">
-        <v>2078.770458384804</v>
+        <v>2087.47677811618</v>
       </c>
       <c r="G2">
         <v>6000</v>
@@ -509,13 +509,13 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>1920.69952928994</v>
+        <v>1938.71455664308</v>
       </c>
       <c r="E3">
-        <v>1683.781841405284</v>
+        <v>1718.20504236414</v>
       </c>
       <c r="F3">
-        <v>2181.211737133239</v>
+        <v>2188.08207524227</v>
       </c>
       <c r="G3">
         <v>6000</v>
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>1905.28063232423</v>
+        <v>1830.77314894047</v>
       </c>
       <c r="E4">
-        <v>1295.92039717895</v>
+        <v>1239.93669411971</v>
       </c>
       <c r="F4">
-        <v>2748.64493962449</v>
+        <v>2746.238488717509</v>
       </c>
       <c r="G4">
         <v>6000</v>
@@ -555,13 +555,13 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>1509.19386341416</v>
+        <v>1603.637205266565</v>
       </c>
       <c r="E5">
-        <v>1105.958808609553</v>
+        <v>1196.33123632338</v>
       </c>
       <c r="F5">
-        <v>2137.24943536719</v>
+        <v>2207.32400365681</v>
       </c>
       <c r="G5">
         <v>6000</v>
@@ -578,13 +578,13 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>1680.239370685315</v>
+        <v>1747.23836191874</v>
       </c>
       <c r="E6">
-        <v>1337.84500257344</v>
+        <v>1416.976382931666</v>
       </c>
       <c r="F6">
-        <v>2072.26952522193</v>
+        <v>2134.61477108738</v>
       </c>
       <c r="G6">
         <v>6000</v>
@@ -601,13 +601,13 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <v>1907.976256733</v>
+        <v>1931.369144575585</v>
       </c>
       <c r="E7">
-        <v>1669.163054643006</v>
+        <v>1695.61932040972</v>
       </c>
       <c r="F7">
-        <v>2176.95024837607</v>
+        <v>2210.8156400671</v>
       </c>
       <c r="G7">
         <v>6000</v>
@@ -624,13 +624,13 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>1823.22707232206</v>
+        <v>1791.17962307884</v>
       </c>
       <c r="E8">
-        <v>1236.606279263052</v>
+        <v>1252.797201096965</v>
       </c>
       <c r="F8">
-        <v>2771.63846275837</v>
+        <v>2656.61969601529</v>
       </c>
       <c r="G8">
         <v>6000</v>
@@ -647,13 +647,13 @@
         <v>15</v>
       </c>
       <c r="D9">
-        <v>1661.14407908697</v>
+        <v>1774.02892791802</v>
       </c>
       <c r="E9">
-        <v>1257.40589568261</v>
+        <v>1354.43149765361</v>
       </c>
       <c r="F9">
-        <v>2298.73873257972</v>
+        <v>2400.50024147665</v>
       </c>
       <c r="G9">
         <v>6000</v>
@@ -670,13 +670,13 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>1708.36195530609</v>
+        <v>1793.006756094855</v>
       </c>
       <c r="E10">
-        <v>1379.75152781912</v>
+        <v>1474.910683508724</v>
       </c>
       <c r="F10">
-        <v>2085.6583110044</v>
+        <v>2190.52236060442</v>
       </c>
       <c r="G10">
         <v>6000</v>
@@ -693,13 +693,13 @@
         <v>11</v>
       </c>
       <c r="D11">
-        <v>1949.51835765636</v>
+        <v>1966.05389237761</v>
       </c>
       <c r="E11">
-        <v>1683.254645586574</v>
+        <v>1719.78415967083</v>
       </c>
       <c r="F11">
-        <v>2233.09483066826</v>
+        <v>2231.39314198428</v>
       </c>
       <c r="G11">
         <v>6000</v>
@@ -716,13 +716,13 @@
         <v>13</v>
       </c>
       <c r="D12">
-        <v>1848.5244396762</v>
+        <v>1861.73623087796</v>
       </c>
       <c r="E12">
-        <v>1271.212896572069</v>
+        <v>1283.86242899673</v>
       </c>
       <c r="F12">
-        <v>2802.74923966572</v>
+        <v>2712.546155937905</v>
       </c>
       <c r="G12">
         <v>6000</v>
@@ -739,13 +739,13 @@
         <v>15</v>
       </c>
       <c r="D13">
-        <v>1595.08738026127</v>
+        <v>1818.628757374975</v>
       </c>
       <c r="E13">
-        <v>1161.822316106932</v>
+        <v>1426.04099776232</v>
       </c>
       <c r="F13">
-        <v>2253.38604822688</v>
+        <v>2435.05114239086</v>
       </c>
       <c r="G13">
         <v>6000</v>
@@ -762,13 +762,13 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>1678.9510387947</v>
+        <v>1750.684231740745</v>
       </c>
       <c r="E14">
-        <v>1365.273451346336</v>
+        <v>1439.12179850613</v>
       </c>
       <c r="F14">
-        <v>2069.71664611423</v>
+        <v>2157.105951144644</v>
       </c>
       <c r="G14">
         <v>6000</v>
@@ -785,13 +785,13 @@
         <v>11</v>
       </c>
       <c r="D15">
-        <v>1927.90827336451</v>
+        <v>1948.45262315996</v>
       </c>
       <c r="E15">
-        <v>1671.07898622216</v>
+        <v>1719.540377190576</v>
       </c>
       <c r="F15">
-        <v>2208.55017897042</v>
+        <v>2201.03620973515</v>
       </c>
       <c r="G15">
         <v>6000</v>
@@ -808,13 +808,13 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <v>1738.882909077935</v>
+        <v>1836.73413472239</v>
       </c>
       <c r="E16">
-        <v>1156.459866758332</v>
+        <v>1222.88414108168</v>
       </c>
       <c r="F16">
-        <v>2683.810562105051</v>
+        <v>2758.241252336022</v>
       </c>
       <c r="G16">
         <v>6000</v>
@@ -831,13 +831,13 @@
         <v>15</v>
       </c>
       <c r="D17">
-        <v>1778.19401436755</v>
+        <v>1756.83554141874</v>
       </c>
       <c r="E17">
-        <v>1395.71950887412</v>
+        <v>1350.891563509313</v>
       </c>
       <c r="F17">
-        <v>2441.37156360483</v>
+        <v>2350.88014644271</v>
       </c>
       <c r="G17">
         <v>6000</v>

--- a/Catch models/msy_resumo_cenarios_cmsy.xlsx
+++ b/Catch models/msy_resumo_cenarios_cmsy.xlsx
@@ -486,13 +486,13 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>1714.805965986315</v>
+        <v>1758.56096709357</v>
       </c>
       <c r="E2">
-        <v>1378.98162613127</v>
+        <v>1442.892397464188</v>
       </c>
       <c r="F2">
-        <v>2087.47677811618</v>
+        <v>2131.20187724156</v>
       </c>
       <c r="G2">
         <v>6000</v>
@@ -509,13 +509,13 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>1938.71455664308</v>
+        <v>1951.02305806997</v>
       </c>
       <c r="E3">
-        <v>1718.20504236414</v>
+        <v>1702.95514700775</v>
       </c>
       <c r="F3">
-        <v>2188.08207524227</v>
+        <v>2222.48304022799</v>
       </c>
       <c r="G3">
         <v>6000</v>
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>1830.77314894047</v>
+        <v>1740.97215100689</v>
       </c>
       <c r="E4">
-        <v>1239.93669411971</v>
+        <v>1188.987356837226</v>
       </c>
       <c r="F4">
-        <v>2746.238488717509</v>
+        <v>2609.559925587997</v>
       </c>
       <c r="G4">
         <v>6000</v>
@@ -555,13 +555,13 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>1603.637205266565</v>
+        <v>1620.645125263315</v>
       </c>
       <c r="E5">
-        <v>1196.33123632338</v>
+        <v>1226.969826634589</v>
       </c>
       <c r="F5">
-        <v>2207.32400365681</v>
+        <v>2201.595323582487</v>
       </c>
       <c r="G5">
         <v>6000</v>
@@ -578,13 +578,13 @@
         <v>9</v>
       </c>
       <c r="D6">
-        <v>1747.23836191874</v>
+        <v>1770.96262160207</v>
       </c>
       <c r="E6">
-        <v>1416.976382931666</v>
+        <v>1450.48195111307</v>
       </c>
       <c r="F6">
-        <v>2134.61477108738</v>
+        <v>2139.49611258724</v>
       </c>
       <c r="G6">
         <v>6000</v>
@@ -601,13 +601,13 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <v>1931.369144575585</v>
+        <v>1945.14744758846</v>
       </c>
       <c r="E7">
-        <v>1695.61932040972</v>
+        <v>1697.05172689376</v>
       </c>
       <c r="F7">
-        <v>2210.8156400671</v>
+        <v>2181.89593511956</v>
       </c>
       <c r="G7">
         <v>6000</v>
@@ -624,13 +624,13 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>1791.17962307884</v>
+        <v>1815.01332305496</v>
       </c>
       <c r="E8">
-        <v>1252.797201096965</v>
+        <v>1226.91439985574</v>
       </c>
       <c r="F8">
-        <v>2656.61969601529</v>
+        <v>2709.505930619173</v>
       </c>
       <c r="G8">
         <v>6000</v>
@@ -647,13 +647,13 @@
         <v>15</v>
       </c>
       <c r="D9">
-        <v>1774.02892791802</v>
+        <v>1750.2238718354</v>
       </c>
       <c r="E9">
-        <v>1354.43149765361</v>
+        <v>1381.27766844203</v>
       </c>
       <c r="F9">
-        <v>2400.50024147665</v>
+        <v>2361.83377676181</v>
       </c>
       <c r="G9">
         <v>6000</v>
@@ -670,13 +670,13 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>1793.006756094855</v>
+        <v>1798.06337601109</v>
       </c>
       <c r="E10">
-        <v>1474.910683508724</v>
+        <v>1467.45383028184</v>
       </c>
       <c r="F10">
-        <v>2190.52236060442</v>
+        <v>2169.52002807255</v>
       </c>
       <c r="G10">
         <v>6000</v>
@@ -693,13 +693,13 @@
         <v>11</v>
       </c>
       <c r="D11">
-        <v>1966.05389237761</v>
+        <v>1964.65343733088</v>
       </c>
       <c r="E11">
-        <v>1719.78415967083</v>
+        <v>1736.98580912124</v>
       </c>
       <c r="F11">
-        <v>2231.39314198428</v>
+        <v>2236.41625259384</v>
       </c>
       <c r="G11">
         <v>6000</v>
@@ -716,13 +716,13 @@
         <v>13</v>
       </c>
       <c r="D12">
-        <v>1861.73623087796</v>
+        <v>2036.67356965293</v>
       </c>
       <c r="E12">
-        <v>1283.86242899673</v>
+        <v>1495.52520151897</v>
       </c>
       <c r="F12">
-        <v>2712.546155937905</v>
+        <v>2848.063190676628</v>
       </c>
       <c r="G12">
         <v>6000</v>
@@ -739,13 +739,13 @@
         <v>15</v>
       </c>
       <c r="D13">
-        <v>1818.628757374975</v>
+        <v>1761.71916394621</v>
       </c>
       <c r="E13">
-        <v>1426.04099776232</v>
+        <v>1356.29074303821</v>
       </c>
       <c r="F13">
-        <v>2435.05114239086</v>
+        <v>2357.46133250453</v>
       </c>
       <c r="G13">
         <v>6000</v>
@@ -762,13 +762,13 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>1750.684231740745</v>
+        <v>1754.791593590925</v>
       </c>
       <c r="E14">
-        <v>1439.12179850613</v>
+        <v>1436.96691555494</v>
       </c>
       <c r="F14">
-        <v>2157.105951144644</v>
+        <v>2131.72916780069</v>
       </c>
       <c r="G14">
         <v>6000</v>
@@ -785,13 +785,13 @@
         <v>11</v>
       </c>
       <c r="D15">
-        <v>1948.45262315996</v>
+        <v>1950.1610830233</v>
       </c>
       <c r="E15">
-        <v>1719.540377190576</v>
+        <v>1715.09483272365</v>
       </c>
       <c r="F15">
-        <v>2201.03620973515</v>
+        <v>2219.173221350629</v>
       </c>
       <c r="G15">
         <v>6000</v>
@@ -808,13 +808,13 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <v>1836.73413472239</v>
+        <v>1740.24803887299</v>
       </c>
       <c r="E16">
-        <v>1222.88414108168</v>
+        <v>1192.586076503815</v>
       </c>
       <c r="F16">
-        <v>2758.241252336022</v>
+        <v>2603.412103060338</v>
       </c>
       <c r="G16">
         <v>6000</v>
@@ -831,13 +831,13 @@
         <v>15</v>
       </c>
       <c r="D17">
-        <v>1756.83554141874</v>
+        <v>1608.97476859164</v>
       </c>
       <c r="E17">
-        <v>1350.891563509313</v>
+        <v>1193.218977593197</v>
       </c>
       <c r="F17">
-        <v>2350.88014644271</v>
+        <v>2197.017130561715</v>
       </c>
       <c r="G17">
         <v>6000</v>
